--- a/AAII_Financials/Yearly/MSGE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MSGE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="92">
   <si>
     <t>MSGE</t>
   </si>
@@ -656,52 +656,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44012</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
@@ -720,33 +720,36 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>1060800</v>
+      </c>
+      <c r="E8" s="3">
         <v>942700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>959300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>851500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>653500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>81800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>584600</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
@@ -765,33 +768,36 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>558600</v>
+      </c>
+      <c r="E9" s="3">
         <v>512500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>547000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>478900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>394800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>75900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>360300</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
@@ -810,33 +816,36 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>502200</v>
+      </c>
+      <c r="E10" s="3">
         <v>430200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>412200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>372600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>258700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>224300</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,9 +864,12 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,8 +887,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,33 +980,36 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E14" s="3">
         <v>18300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>18900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-14000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>90600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-36500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-278400</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1009,38 +1028,41 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E15" s="3">
         <v>57800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>53900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>60500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>69500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>71600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>81600</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
@@ -1054,9 +1076,12 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,32 +1096,33 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>893200</v>
+      </c>
+      <c r="E17" s="3">
         <v>810900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>833100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>744000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>653100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>304700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>601400</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1115,33 +1141,36 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>167600</v>
+      </c>
+      <c r="E18" s="3">
         <v>131800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>126100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>107500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-222900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-16800</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1160,9 +1189,12 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,32 +1212,33 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-900</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-900</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1224,38 +1257,41 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>223700</v>
+      </c>
+      <c r="E21" s="3">
         <v>189800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>180000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>168900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>69900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-151600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>65600</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
       <c r="K21" s="3">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
+      <c r="L21" s="3">
+        <v>0</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
@@ -1269,33 +1305,36 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>40000</v>
+      </c>
+      <c r="E22" s="3">
         <v>50500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>58000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>51900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>53100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>33700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>400</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1314,33 +1353,36 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E23" s="3">
         <v>65600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>52300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>77800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-136300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-214000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>270800</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1359,33 +1401,36 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>40800</v>
+      </c>
+      <c r="E24" s="3">
         <v>28100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-92000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100200</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1404,9 +1449,12 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,33 +1497,36 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E26" s="3">
         <v>37400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>144300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>76000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-136200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-219300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>170700</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1494,33 +1545,36 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E27" s="3">
         <v>37400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>144300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>76600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-133300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-218600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>171700</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,9 +1593,12 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,33 +1785,36 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>900</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>900</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1764,33 +1833,36 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E33" s="3">
         <v>37400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>144300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>76600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-133300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-218600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>171700</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,9 +1881,12 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,33 +1929,36 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E35" s="3">
         <v>37400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>144300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>76600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-133300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-218600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>171700</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1899,38 +1977,41 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44012</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1949,9 +2030,12 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,29 +2073,30 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>293600</v>
+      </c>
+      <c r="E41" s="3">
         <v>43000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>33300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>76100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>58100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>317800</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2032,9 +2118,12 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2065,8 +2154,8 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
+      <c r="M42" s="3">
+        <v>0</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
@@ -2077,30 +2166,33 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>124500</v>
+      </c>
+      <c r="E43" s="3">
         <v>96900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>102600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>144600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>204900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>170300</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,30 +2214,33 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E44" s="3">
         <v>3800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2200</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2155,8 +2250,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2167,30 +2262,33 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E45" s="3">
         <v>3900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7700</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2212,30 +2310,33 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>522100</v>
+      </c>
+      <c r="E46" s="3">
         <v>237100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>219100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>295300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>341500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>544800</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2257,30 +2358,33 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E47" s="3">
         <v>7100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>35100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>36400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>86300</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2302,30 +2406,33 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1040600</v>
+      </c>
+      <c r="E48" s="3">
         <v>1105600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1022200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>864700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>967200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>838700</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2347,9 +2454,12 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2363,16 +2473,16 @@
         <v>132800</v>
       </c>
       <c r="G49" s="3">
+        <v>132800</v>
+      </c>
+      <c r="H49" s="3">
         <v>134500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>140300</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2392,9 +2502,12 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,30 +2598,33 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E52" s="3">
         <v>1900</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1800</v>
       </c>
       <c r="F52" s="3">
         <v>1800</v>
       </c>
       <c r="G52" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H52" s="3">
         <v>2600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>20300</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2527,9 +2646,12 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,30 +2694,33 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1935300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1669800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1552700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1401200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1526700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1697300</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2617,9 +2742,12 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,29 +2785,30 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E57" s="3">
         <v>12100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>26600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2500</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,32 +2830,35 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>74900</v>
+      </c>
+      <c r="E58" s="3">
         <v>65600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>44000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>52800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>47800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>47400</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2745,30 +2878,33 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>537900</v>
+      </c>
+      <c r="E59" s="3">
         <v>328900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>325800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>363700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>353800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>294200</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,30 +2926,33 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>748300</v>
+      </c>
+      <c r="E60" s="3">
         <v>502400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>505800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>540600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>545100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>429200</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2835,30 +2974,33 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1100400</v>
+      </c>
+      <c r="E61" s="3">
         <v>1135300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1026300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>850100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>909000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>688500</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2880,30 +3022,33 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E62" s="3">
         <v>32500</v>
-      </c>
-      <c r="E62" s="3">
-        <v>25900</v>
       </c>
       <c r="F62" s="3">
         <v>25900</v>
       </c>
       <c r="G62" s="3">
+        <v>25900</v>
+      </c>
+      <c r="H62" s="3">
         <v>50900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>57600</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2925,9 +3070,12 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,30 +3214,33 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1889500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1683100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1575900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1470600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1528300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1198600</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3105,9 +3262,12 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,24 +3474,27 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>219200</v>
+      </c>
+      <c r="E72" s="3">
         <v>153000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>115600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-28700</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3346,12 +3519,15 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3">
+        <v>0</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,30 +3666,33 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-13300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-23200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-69500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>495900</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3529,9 +3714,12 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,38 +3762,41 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44012</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3624,33 +3815,36 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>66200</v>
+      </c>
+      <c r="E81" s="3">
         <v>37400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>144300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>76600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-133300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-218600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>171700</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3669,9 +3863,12 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,32 +3886,33 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E83" s="3">
         <v>57800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>53900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>59700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>63700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>70600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>87100</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3733,9 +3931,12 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,33 +4171,36 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>351400</v>
+      </c>
+      <c r="E89" s="3">
         <v>115300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>111300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>135700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>95400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-148100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>31500</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4003,9 +4219,12 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,32 +4242,33 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-22200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-24200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-29600</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
@@ -4067,9 +4287,12 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,33 +4383,36 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-23700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-62400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>30300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>45400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>276400</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4202,9 +4431,12 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,8 +4454,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,33 +4643,36 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-81600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-99700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-144200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-396300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>473500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-315400</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4446,9 +4691,12 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4476,11 +4724,11 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
@@ -4491,38 +4739,41 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>250600</v>
+      </c>
+      <c r="E102" s="3">
         <v>10000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-50800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>21800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-255500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>315000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7500</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
@@ -4536,7 +4787,10 @@
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
